--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_332_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_332_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M2" t="n">
         <v>6</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M3" t="n">
         <v>9</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1534,13 +1534,13 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X18" t="n">
         <v>3</v>
@@ -1733,10 +1733,10 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>2</v>
@@ -2315,10 +2315,10 @@
         <v>21</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2517,10 +2517,10 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X23" t="n">
         <v>2</v>
@@ -2710,13 +2710,13 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X24" t="n">
         <v>7</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3099,7 +3099,7 @@
         <v>8</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -3295,10 +3295,10 @@
         <v>11</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3491,16 +3491,16 @@
         <v>25</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X28" t="n">
         <v>9</v>
@@ -3827,16 +3827,16 @@
         <v>120</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X30" t="n">
         <v>36</v>
@@ -4494,10 +4494,10 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
@@ -4880,7 +4880,7 @@
         <v>14</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -5076,10 +5076,10 @@
         <v>20</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -5278,10 +5278,10 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X41" t="n">
         <v>1</v>
@@ -6062,10 +6062,10 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X44" t="n">
         <v>4</v>
@@ -6255,13 +6255,13 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X45" t="n">
         <v>6</v>
@@ -6454,10 +6454,10 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X46" t="n">
         <v>5</v>
@@ -6784,16 +6784,16 @@
         <v>107</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X48" t="n">
         <v>26</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_332_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_332_EL.xlsx
@@ -674,10 +674,10 @@
         <v>6</v>
       </c>
       <c r="N2" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="O2" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="P2" t="n">
         <v>3</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>73.47</t>
+          <t>58.06</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>9</v>
       </c>
       <c r="N3" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="O3" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="P3" t="n">
         <v>3</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>92.86</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1543,14 +1543,14 @@
         <v>2</v>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA18" t="n">
@@ -1935,14 +1935,14 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA20" t="n">
@@ -2327,14 +2327,14 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="n">
         <v>3</v>
       </c>
-      <c r="Y22" t="n">
-        <v>5</v>
-      </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA22" t="n">
@@ -2719,14 +2719,14 @@
         <v>2</v>
       </c>
       <c r="X24" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA24" t="n">
@@ -3503,14 +3503,14 @@
         <v>2</v>
       </c>
       <c r="X28" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Y28" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA28" t="n">
@@ -3839,14 +3839,14 @@
         <v>9</v>
       </c>
       <c r="X30" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="Y30" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4696,10 +4696,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -4892,10 +4892,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
@@ -5088,14 +5088,14 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y39" t="n">
         <v>3</v>
       </c>
-      <c r="Y39" t="n">
-        <v>4</v>
-      </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA39" t="n">
@@ -6068,10 +6068,10 @@
         <v>3</v>
       </c>
       <c r="X44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -6264,10 +6264,10 @@
         <v>1</v>
       </c>
       <c r="X45" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y45" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
@@ -6460,10 +6460,10 @@
         <v>1</v>
       </c>
       <c r="X46" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y46" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
@@ -6796,14 +6796,14 @@
         <v>8</v>
       </c>
       <c r="X48" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="Y48" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>88.2%</t>
         </is>
       </c>
       <c r="AA48" t="n">
